--- a/tools/importer/reports/import-zipcode-gate-login.report.xlsx
+++ b/tools/importer/reports/import-zipcode-gate-login.report.xlsx
@@ -283,13 +283,13 @@
     <t>zipcode-gate-login.report.json</t>
   </si>
   <si>
-    <t>["zip-county-form"]</t>
+    <t>["zip-county-form","accordion-minimal-light"]</t>
   </si>
   <si>
     <t>zipcode-gate-login</t>
   </si>
   <si>
-    <t>2026-10-05T16:34:47.859Z</t>
+    <t>2026-10-06T11:01:05.594Z</t>
   </si>
   <si>
     <t>https://www.highmark.com/zipcode-gate-login</t>
